--- a/bulk upload format.xlsx
+++ b/bulk upload format.xlsx
@@ -1873,9 +1873,8 @@
   <dimension ref="A1:H218"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="54.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" style="14"/>
-    <col min="4" max="4" width="10.81640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.81640625" style="14" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1886,11 +1885,11 @@
       <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>4</v>
